--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Mistral-7B-Instruct-v0.3/metrics_default_vs_simple.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Mistral-7B-Instruct-v0.3/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.3888888888888889</v>
+        <v>0.3775510204081632</v>
       </c>
       <c r="B2">
-        <v>0.07692307692307693</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="C2">
-        <v>0.4507042253521127</v>
+        <v>0.4788732394366197</v>
       </c>
       <c r="D2">
-        <v>0.6446280991735537</v>
+        <v>0.6548672566371682</v>
       </c>
       <c r="E2">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
